--- a/dados_projeto.xlsx
+++ b/dados_projeto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E212"/>
+  <dimension ref="A1:G212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,16 @@
           <t>Preço Total</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -450,9 +460,21 @@
           <t>Fogão Cooktop</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -461,9 +483,21 @@
           <t>Geladeira</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -472,9 +506,21 @@
           <t>Microondas</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -483,9 +529,21 @@
           <t>Liquidificador</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -494,9 +552,21 @@
           <t>Mixer</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -505,9 +575,21 @@
           <t>Espremedor de Laranja</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -516,9 +598,21 @@
           <t>Sanduicheira</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -527,9 +621,21 @@
           <t>Panela de Arroz Elétrica</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -538,9 +644,21 @@
           <t>Panela de Pressão Elétrica</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -549,9 +667,21 @@
           <t>Lava Louça</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -560,9 +690,21 @@
           <t>Torneira Elétrica</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -571,9 +713,21 @@
           <t>Churrasqueira Elétrica</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -582,9 +736,21 @@
           <t>Jarra Elétrica</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -593,9 +759,21 @@
           <t>Batedeira</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -604,9 +782,21 @@
           <t>Forno Elétrico</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -615,9 +805,21 @@
           <t>Air Fryer</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -626,9 +828,21 @@
           <t>Torradeira</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -637,9 +851,21 @@
           <t>Cafeteira</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -648,9 +874,21 @@
           <t>Suggar/Coifa</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -659,9 +897,21 @@
           <t>Purificador de Água</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -670,9 +920,21 @@
           <t>TV</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -681,9 +943,21 @@
           <t>Alexa</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -692,9 +966,21 @@
           <t>Fita de Led</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -703,9 +989,21 @@
           <t>Fechadura eletrônica</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -714,9 +1012,21 @@
           <t>Interruptores inteligentes</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -725,9 +1035,21 @@
           <t>Tomada inteligente</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -736,9 +1058,21 @@
           <t>Ventilador</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -747,9 +1081,21 @@
           <t>Ar Condicionado</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -758,9 +1104,21 @@
           <t>Ferro de passar roupas</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -769,9 +1127,21 @@
           <t>Pipoqueira</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -780,9 +1150,21 @@
           <t>Jogo de panelas</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -791,9 +1173,21 @@
           <t>Jogo de frigideiras</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -802,9 +1196,21 @@
           <t>Panela de pressão</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -813,9 +1219,21 @@
           <t>Jogo de talheres</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -824,9 +1242,21 @@
           <t>Faqueiro</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -835,9 +1265,21 @@
           <t>Jogo de jantar</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -846,9 +1288,21 @@
           <t>Jogo copos</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -857,9 +1311,21 @@
           <t>Jogo de xícaras p/café</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -868,9 +1334,21 @@
           <t>Jogo de taças p/ vinho</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -879,9 +1357,21 @@
           <t>Jogo taças p/ águá e suco</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -890,9 +1380,21 @@
           <t>Jogo sobremesa</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -901,9 +1403,21 @@
           <t>Canecas</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -912,9 +1426,21 @@
           <t>Porta temperos</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -923,9 +1449,21 @@
           <t>Tábua de corte</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -934,9 +1472,21 @@
           <t>Descanso de panela</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -945,9 +1495,21 @@
           <t>Potes porta mantimentos</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -956,9 +1518,21 @@
           <t>Escorredor de louça</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -967,9 +1541,21 @@
           <t>Escova de limpeza</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -978,9 +1564,21 @@
           <t>Ralador</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -989,9 +1587,21 @@
           <t>Peneira</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -1000,9 +1610,21 @@
           <t>Saleiro</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -1011,9 +1633,21 @@
           <t>Chaleira</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -1022,9 +1656,21 @@
           <t>Leiteira</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -1033,9 +1679,21 @@
           <t>Abridor de vinho</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -1044,9 +1702,21 @@
           <t>Travessa de vidro</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -1055,9 +1725,21 @@
           <t>Porta pão</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -1066,9 +1748,21 @@
           <t>Afiador de facas</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -1077,9 +1771,21 @@
           <t>Galheteiros</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -1088,9 +1794,21 @@
           <t>Porta copos</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -1099,9 +1817,21 @@
           <t>Saleiro p/ mesa</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -1110,9 +1840,21 @@
           <t>Medidores</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -1121,9 +1863,21 @@
           <t>Abridor de garrafas</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -1132,9 +1886,21 @@
           <t>Porta frios</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -1143,9 +1909,21 @@
           <t>Jogo americano</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -1154,9 +1932,21 @@
           <t>Porta palito</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -1165,9 +1955,21 @@
           <t>Mantegueira</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -1176,9 +1978,21 @@
           <t>Torneira gourmet</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -1187,9 +2001,21 @@
           <t>Cortador de pizza</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -1198,9 +2024,21 @@
           <t>Secador de Saladas</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -1209,9 +2047,21 @@
           <t>Forma de Gelo</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -1220,9 +2070,21 @@
           <t>Colher de Sorvete</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -1231,9 +2093,21 @@
           <t>Açucareiro</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -1242,9 +2116,21 @@
           <t>Abridor de latas</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -1253,9 +2139,21 @@
           <t>Prendedor de embalagem</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -1264,9 +2162,21 @@
           <t>Organizador de geladeira</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -1275,9 +2185,21 @@
           <t>Escorredor de Massa</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -1286,9 +2208,21 @@
           <t>Fruteira</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -1297,9 +2231,21 @@
           <t>Luva térmica</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -1308,9 +2254,21 @@
           <t>Garrafa de água</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
@@ -1319,9 +2277,21 @@
           <t>Rolo de massa</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
@@ -1330,9 +2300,21 @@
           <t>Moedor de pimenta</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
@@ -1341,9 +2323,21 @@
           <t>Queijeira</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
@@ -1352,9 +2346,21 @@
           <t>Colher de pau</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
@@ -1363,9 +2369,21 @@
           <t>Aparelho fundue</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
@@ -1374,9 +2392,21 @@
           <t>Saladeira</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
@@ -1385,9 +2415,21 @@
           <t>Forma silicone airfryer</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
@@ -1396,9 +2438,21 @@
           <t>Porta guardanapo</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
@@ -1407,9 +2461,21 @@
           <t>Porta alho</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
@@ -1418,9 +2484,21 @@
           <t>Processador de alimentos</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
@@ -1429,9 +2507,21 @@
           <t>Bandeja café da manhã</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -1440,9 +2530,21 @@
           <t>Forma de pudim</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -1451,9 +2553,21 @@
           <t>Forma de pão</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
@@ -1462,9 +2576,21 @@
           <t>Forma de pizza</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
@@ -1473,9 +2599,21 @@
           <t>Garrafa térmica</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
@@ -1484,9 +2622,21 @@
           <t>Estátula para bolo</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
@@ -1495,9 +2645,21 @@
           <t>Copo medidor</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
@@ -1506,9 +2668,21 @@
           <t>Porta detergente</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
@@ -1517,9 +2691,21 @@
           <t>Panos de prato</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -1528,9 +2714,21 @@
           <t>Pano de pia/micro fibra</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
@@ -1539,9 +2737,21 @@
           <t>Rodo de pia</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -1550,9 +2760,21 @@
           <t>Jarra de suco</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
@@ -1561,9 +2783,21 @@
           <t>Bowls</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
@@ -1572,9 +2806,21 @@
           <t>Tábuas de madeira</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
@@ -1583,9 +2829,21 @@
           <t>Petisqueira</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -1594,9 +2852,21 @@
           <t>Espremedor (limão/alho)</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
@@ -1605,9 +2875,21 @@
           <t>Amassador de Bife</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -1616,9 +2898,21 @@
           <t>Suporte papel toalha</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
@@ -1627,9 +2921,21 @@
           <t>Suporte plástico filme</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
@@ -1638,9 +2944,21 @@
           <t>Boleira</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -1649,9 +2967,21 @@
           <t>Porta café</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
@@ -1660,9 +2990,21 @@
           <t>Fuet</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
@@ -1671,9 +3013,21 @@
           <t>Descanso de colher</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
@@ -1682,9 +3036,21 @@
           <t>Kit copo cerveja</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
@@ -1693,9 +3059,21 @@
           <t>Potes de vidro</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
@@ -1704,9 +3082,21 @@
           <t>Frigideira grande</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -1715,9 +3105,21 @@
           <t>Potinhos de porcelana</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
@@ -1726,9 +3128,21 @@
           <t>Potes herméticos</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
@@ -1737,9 +3151,21 @@
           <t>Desfiador de frango manual</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -1748,9 +3174,21 @@
           <t>Taças Milk Shake</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
@@ -1759,9 +3197,21 @@
           <t>Cuia</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
@@ -1770,9 +3220,21 @@
           <t>Bomba de chimarrão</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
@@ -1781,9 +3243,21 @@
           <t>Mateira</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
@@ -1792,9 +3266,21 @@
           <t>Coador de café</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
@@ -1803,9 +3289,21 @@
           <t>Pegador de Massa</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
@@ -1814,9 +3312,21 @@
           <t>Cafeteira Italiana</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
@@ -1825,9 +3335,21 @@
           <t>Vassoura</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
@@ -1836,9 +3358,21 @@
           <t>Aspirador de pó</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
@@ -1847,9 +3381,21 @@
           <t>Moop limpeza</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
@@ -1858,9 +3404,21 @@
           <t>Rodo</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
@@ -1869,9 +3427,21 @@
           <t>Baldes</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -1880,9 +3450,21 @@
           <t>Bacia</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
@@ -1891,9 +3473,21 @@
           <t>Cesto de roupas</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
@@ -1902,9 +3496,21 @@
           <t>Prendedores de roupas</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
@@ -1913,9 +3519,21 @@
           <t>Panos de chão</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
@@ -1924,9 +3542,21 @@
           <t>Panos micro fibra</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
@@ -1935,9 +3565,21 @@
           <t>Organizadores p/ produtos</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
@@ -1946,9 +3588,21 @@
           <t>Escova de limpeza</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
@@ -1957,9 +3611,21 @@
           <t>Pá de lixo</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
@@ -1968,9 +3634,21 @@
           <t>Escada doméstica</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -1979,9 +3657,21 @@
           <t>Ferro de passar</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
@@ -1990,9 +3680,21 @@
           <t>Robo aspirador</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
@@ -2001,9 +3703,21 @@
           <t>Desentupidor de Pia</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
@@ -2012,9 +3726,21 @@
           <t>Varal de chão</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -2023,9 +3749,21 @@
           <t>Mop Spray</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
@@ -2034,9 +3772,21 @@
           <t>Mop limpeza pesada</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
@@ -2045,9 +3795,21 @@
           <t>Chuveiro</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
@@ -2056,9 +3818,21 @@
           <t>Box de vidro</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
@@ -2067,9 +3841,21 @@
           <t>Espelho</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
@@ -2078,9 +3864,21 @@
           <t>Saboneteira</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
@@ -2089,9 +3887,21 @@
           <t>Lixeira</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -2100,9 +3910,21 @@
           <t>Toalhas de banho</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
@@ -2111,9 +3933,21 @@
           <t>Toalhas de rosto</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
@@ -2122,9 +3956,21 @@
           <t>Toalha para os pés</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
@@ -2133,9 +3979,21 @@
           <t>Tapete anti derapante</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
@@ -2144,9 +4002,21 @@
           <t>Escova sanitária</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
@@ -2155,9 +4025,21 @@
           <t>Kit lavabo</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
@@ -2166,9 +4048,21 @@
           <t>Kit porta toalhas</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
@@ -2177,9 +4071,21 @@
           <t>Porta papel higiênico</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
@@ -2188,9 +4094,21 @@
           <t>Registros</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
@@ -2199,9 +4117,21 @@
           <t>Torneira</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -2210,9 +4140,21 @@
           <t>Armário</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
@@ -2221,9 +4163,21 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
@@ -2232,9 +4186,21 @@
           <t>Cortina p/ box</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -2243,9 +4209,21 @@
           <t>Tapete Box</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
@@ -2254,9 +4232,21 @@
           <t>Toalha pés</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -2265,9 +4255,21 @@
           <t>Cama Box/ Colchão</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -2276,9 +4278,21 @@
           <t>Guarda roupas</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -2287,9 +4301,21 @@
           <t>Espelho</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
@@ -2298,9 +4324,21 @@
           <t>Penteadeira</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -2309,9 +4347,21 @@
           <t>Suporte para tv</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
@@ -2320,9 +4370,21 @@
           <t>Cortina blackout</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
@@ -2331,9 +4393,21 @@
           <t>Suporte p/ cortina</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
@@ -2342,9 +4416,21 @@
           <t>Cabeceira</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
@@ -2353,9 +4439,21 @@
           <t>Travesseiros</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
@@ -2364,9 +4462,21 @@
           <t>Almofadas</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
@@ -2375,9 +4485,21 @@
           <t>Manta</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
@@ -2386,9 +4508,21 @@
           <t>Jogo de lençol</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
@@ -2397,9 +4531,21 @@
           <t>Edredom</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
@@ -2408,9 +4554,21 @@
           <t>Cobre leito</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
@@ -2419,9 +4577,21 @@
           <t>Luminária</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
@@ -2430,9 +4600,21 @@
           <t>Roupeiro</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
@@ -2441,9 +4623,21 @@
           <t>Painel de tv</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
@@ -2452,9 +4646,21 @@
           <t>Rack</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
@@ -2463,9 +4669,21 @@
           <t>Cortina</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>
@@ -2474,9 +4692,21 @@
           <t>Sofá</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
@@ -2485,9 +4715,21 @@
           <t>Almofadas decorativas</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
@@ -2496,9 +4738,21 @@
           <t>Quadros</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
@@ -2507,9 +4761,21 @@
           <t>Espelho</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
@@ -2518,9 +4784,21 @@
           <t>Plantas</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
@@ -2529,9 +4807,21 @@
           <t>Itens de decoração</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
@@ -2540,9 +4830,21 @@
           <t>Mesa de Jantar</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
@@ -2551,9 +4853,21 @@
           <t>Cadeiras</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
@@ -2562,9 +4876,21 @@
           <t>Mesa de centro</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
@@ -2573,9 +4899,21 @@
           <t>Barzinho</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>
@@ -2584,9 +4922,21 @@
           <t>Difusor</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
@@ -2595,9 +4945,21 @@
           <t>Organizador de chaves</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
@@ -2606,9 +4968,21 @@
           <t>Tapete de entrada</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
@@ -2617,9 +4991,21 @@
           <t>Tapete sala</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
@@ -2628,9 +5014,21 @@
           <t>Manta para sofá</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
@@ -2639,9 +5037,21 @@
           <t>Prateleira</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
@@ -2650,9 +5060,21 @@
           <t>Lâmpadas</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
@@ -2661,9 +5083,21 @@
           <t>Plafon (suporte lâmpada)</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
@@ -2672,9 +5106,21 @@
           <t>Caixinha de remédios</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
@@ -2683,9 +5129,21 @@
           <t>Fita métrica</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
@@ -2694,9 +5152,21 @@
           <t>Balança</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
@@ -2705,9 +5175,21 @@
           <t>Fita isolante</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
@@ -2716,9 +5198,21 @@
           <t>Maleta de ferramentas</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
@@ -2727,9 +5221,21 @@
           <t>Furadeira</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
@@ -2738,9 +5244,21 @@
           <t>Tesoura</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
@@ -2749,9 +5267,21 @@
           <t>Velas</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
@@ -2760,9 +5290,21 @@
           <t>Calendário</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_projeto.xlsx
+++ b/dados_projeto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JR\Desktop\Projeto_Enxoval\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9050f00462f35375/Desktop/PYTHON/Projeto_Enxoval/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F9F760-CB75-4513-AE38-A32BB50E1E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{61F9F760-CB75-4513-AE38-A32BB50E1E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DAF5E58-8A92-4FAF-AC12-98532E19C70D}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="219">
   <si>
     <t>Ambiente</t>
   </si>
@@ -529,15 +529,9 @@
     <t>Cuba</t>
   </si>
   <si>
-    <t>Cortina p/ box</t>
-  </si>
-  <si>
     <t>Tapete Box</t>
   </si>
   <si>
-    <t>Toalha pés</t>
-  </si>
-  <si>
     <t>Cama Box/ Colchão</t>
   </si>
   <si>
@@ -671,6 +665,18 @@
   </si>
   <si>
     <t>Cozinha</t>
+  </si>
+  <si>
+    <t>Sala</t>
+  </si>
+  <si>
+    <t>Quarto</t>
+  </si>
+  <si>
+    <t>Lavanderia</t>
+  </si>
+  <si>
+    <t>Banheiro</t>
   </si>
 </sst>
 </file>
@@ -1010,8 +1016,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1038,7 +1048,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -1058,7 +1068,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -1078,7 +1088,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1098,7 +1108,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -1117,6 +1127,9 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>214</v>
+      </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -1134,6 +1147,9 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>214</v>
+      </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -1151,6 +1167,9 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>214</v>
+      </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -1168,6 +1187,9 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>214</v>
+      </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
@@ -1185,6 +1207,9 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>214</v>
+      </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1202,6 +1227,9 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>214</v>
+      </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -1219,6 +1247,9 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>214</v>
+      </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -1236,6 +1267,9 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>214</v>
+      </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
@@ -1253,6 +1287,9 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>214</v>
+      </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
@@ -1270,6 +1307,9 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>214</v>
+      </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
@@ -1287,6 +1327,9 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>214</v>
+      </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
@@ -1303,7 +1346,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>214</v>
+      </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
@@ -1320,7 +1366,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>214</v>
+      </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
@@ -1337,7 +1386,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>214</v>
+      </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
@@ -1354,7 +1406,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>214</v>
+      </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
@@ -1371,7 +1426,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>214</v>
+      </c>
       <c r="B21" t="s">
         <v>27</v>
       </c>
@@ -1388,7 +1446,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>215</v>
+      </c>
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -1405,7 +1466,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>215</v>
+      </c>
       <c r="B23" t="s">
         <v>29</v>
       </c>
@@ -1422,7 +1486,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>215</v>
+      </c>
       <c r="B24" t="s">
         <v>30</v>
       </c>
@@ -1439,7 +1506,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>215</v>
+      </c>
       <c r="B25" t="s">
         <v>31</v>
       </c>
@@ -1456,7 +1526,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>215</v>
+      </c>
       <c r="B26" t="s">
         <v>32</v>
       </c>
@@ -1473,7 +1546,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>215</v>
+      </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
@@ -1490,7 +1566,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>215</v>
+      </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
@@ -1507,7 +1586,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>216</v>
+      </c>
       <c r="B29" t="s">
         <v>35</v>
       </c>
@@ -1524,7 +1606,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>216</v>
+      </c>
       <c r="B30" t="s">
         <v>36</v>
       </c>
@@ -1541,7 +1626,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>214</v>
+      </c>
       <c r="B31" t="s">
         <v>37</v>
       </c>
@@ -1558,7 +1646,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>214</v>
+      </c>
       <c r="B32" t="s">
         <v>38</v>
       </c>
@@ -1575,7 +1666,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>214</v>
+      </c>
       <c r="B33" t="s">
         <v>39</v>
       </c>
@@ -1592,7 +1686,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>214</v>
+      </c>
       <c r="B34" t="s">
         <v>40</v>
       </c>
@@ -1609,7 +1706,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>214</v>
+      </c>
       <c r="B35" t="s">
         <v>41</v>
       </c>
@@ -1626,7 +1726,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>214</v>
+      </c>
       <c r="B36" t="s">
         <v>42</v>
       </c>
@@ -1643,7 +1746,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>214</v>
+      </c>
       <c r="B37" t="s">
         <v>43</v>
       </c>
@@ -1660,7 +1766,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>214</v>
+      </c>
       <c r="B38" t="s">
         <v>44</v>
       </c>
@@ -1677,7 +1786,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>214</v>
+      </c>
       <c r="B39" t="s">
         <v>45</v>
       </c>
@@ -1694,7 +1806,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>214</v>
+      </c>
       <c r="B40" t="s">
         <v>46</v>
       </c>
@@ -1711,7 +1826,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>214</v>
+      </c>
       <c r="B41" t="s">
         <v>47</v>
       </c>
@@ -1728,7 +1846,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>214</v>
+      </c>
       <c r="B42" t="s">
         <v>48</v>
       </c>
@@ -1745,7 +1866,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>214</v>
+      </c>
       <c r="B43" t="s">
         <v>49</v>
       </c>
@@ -1762,7 +1886,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
       <c r="B44" t="s">
         <v>50</v>
       </c>
@@ -1779,7 +1906,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>214</v>
+      </c>
       <c r="B45" t="s">
         <v>51</v>
       </c>
@@ -1796,7 +1926,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>214</v>
+      </c>
       <c r="B46" t="s">
         <v>52</v>
       </c>
@@ -1813,7 +1946,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>214</v>
+      </c>
       <c r="B47" t="s">
         <v>53</v>
       </c>
@@ -1830,7 +1966,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>214</v>
+      </c>
       <c r="B48" t="s">
         <v>54</v>
       </c>
@@ -1847,7 +1986,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>217</v>
+      </c>
       <c r="B49" t="s">
         <v>55</v>
       </c>
@@ -1864,7 +2006,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>214</v>
+      </c>
       <c r="B50" t="s">
         <v>56</v>
       </c>
@@ -1881,7 +2026,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>214</v>
+      </c>
       <c r="B51" t="s">
         <v>57</v>
       </c>
@@ -1898,7 +2046,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>214</v>
+      </c>
       <c r="B52" t="s">
         <v>58</v>
       </c>
@@ -1915,7 +2066,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>214</v>
+      </c>
       <c r="B53" t="s">
         <v>59</v>
       </c>
@@ -1932,7 +2086,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>214</v>
+      </c>
       <c r="B54" t="s">
         <v>60</v>
       </c>
@@ -1949,7 +2106,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>214</v>
+      </c>
       <c r="B55" t="s">
         <v>61</v>
       </c>
@@ -1966,7 +2126,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>214</v>
+      </c>
       <c r="B56" t="s">
         <v>62</v>
       </c>
@@ -1983,7 +2146,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>214</v>
+      </c>
       <c r="B57" t="s">
         <v>63</v>
       </c>
@@ -2000,7 +2166,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>214</v>
+      </c>
       <c r="B58" t="s">
         <v>64</v>
       </c>
@@ -2017,7 +2186,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>214</v>
+      </c>
       <c r="B59" t="s">
         <v>65</v>
       </c>
@@ -2034,7 +2206,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>214</v>
+      </c>
       <c r="B60" t="s">
         <v>66</v>
       </c>
@@ -2051,7 +2226,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>214</v>
+      </c>
       <c r="B61" t="s">
         <v>67</v>
       </c>
@@ -2068,7 +2246,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>214</v>
+      </c>
       <c r="B62" t="s">
         <v>68</v>
       </c>
@@ -2085,7 +2266,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>214</v>
+      </c>
       <c r="B63" t="s">
         <v>69</v>
       </c>
@@ -2102,7 +2286,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>214</v>
+      </c>
       <c r="B64" t="s">
         <v>70</v>
       </c>
@@ -2119,7 +2306,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>214</v>
+      </c>
       <c r="B65" t="s">
         <v>71</v>
       </c>
@@ -2136,7 +2326,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>214</v>
+      </c>
       <c r="B66" t="s">
         <v>72</v>
       </c>
@@ -2153,7 +2346,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>214</v>
+      </c>
       <c r="B67" t="s">
         <v>73</v>
       </c>
@@ -2170,7 +2366,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>214</v>
+      </c>
       <c r="B68" t="s">
         <v>74</v>
       </c>
@@ -2187,7 +2386,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>214</v>
+      </c>
       <c r="B69" t="s">
         <v>75</v>
       </c>
@@ -2204,7 +2406,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>214</v>
+      </c>
       <c r="B70" t="s">
         <v>76</v>
       </c>
@@ -2221,7 +2426,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>214</v>
+      </c>
       <c r="B71" t="s">
         <v>77</v>
       </c>
@@ -2238,7 +2446,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>214</v>
+      </c>
       <c r="B72" t="s">
         <v>78</v>
       </c>
@@ -2255,7 +2466,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>214</v>
+      </c>
       <c r="B73" t="s">
         <v>79</v>
       </c>
@@ -2272,7 +2486,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>214</v>
+      </c>
       <c r="B74" t="s">
         <v>80</v>
       </c>
@@ -2289,7 +2506,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>214</v>
+      </c>
       <c r="B75" t="s">
         <v>81</v>
       </c>
@@ -2306,7 +2526,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>214</v>
+      </c>
       <c r="B76" t="s">
         <v>82</v>
       </c>
@@ -2323,7 +2546,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>214</v>
+      </c>
       <c r="B77" t="s">
         <v>83</v>
       </c>
@@ -2340,7 +2566,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>214</v>
+      </c>
       <c r="B78" t="s">
         <v>84</v>
       </c>
@@ -2357,7 +2586,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>214</v>
+      </c>
       <c r="B79" t="s">
         <v>85</v>
       </c>
@@ -2374,7 +2606,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>214</v>
+      </c>
       <c r="B80" t="s">
         <v>86</v>
       </c>
@@ -2391,7 +2626,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>214</v>
+      </c>
       <c r="B81" t="s">
         <v>87</v>
       </c>
@@ -2408,7 +2646,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>214</v>
+      </c>
       <c r="B82" t="s">
         <v>88</v>
       </c>
@@ -2425,7 +2666,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>214</v>
+      </c>
       <c r="B83" t="s">
         <v>89</v>
       </c>
@@ -2442,7 +2686,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>214</v>
+      </c>
       <c r="B84" t="s">
         <v>90</v>
       </c>
@@ -2459,7 +2706,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>214</v>
+      </c>
       <c r="B85" t="s">
         <v>91</v>
       </c>
@@ -2476,7 +2726,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>214</v>
+      </c>
       <c r="B86" t="s">
         <v>92</v>
       </c>
@@ -2493,7 +2746,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>214</v>
+      </c>
       <c r="B87" t="s">
         <v>93</v>
       </c>
@@ -2510,7 +2766,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>214</v>
+      </c>
       <c r="B88" t="s">
         <v>94</v>
       </c>
@@ -2527,7 +2786,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>214</v>
+      </c>
       <c r="B89" t="s">
         <v>95</v>
       </c>
@@ -2544,7 +2806,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>214</v>
+      </c>
       <c r="B90" t="s">
         <v>96</v>
       </c>
@@ -2561,7 +2826,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>214</v>
+      </c>
       <c r="B91" t="s">
         <v>97</v>
       </c>
@@ -2578,7 +2846,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>214</v>
+      </c>
       <c r="B92" t="s">
         <v>98</v>
       </c>
@@ -2595,7 +2866,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>214</v>
+      </c>
       <c r="B93" t="s">
         <v>99</v>
       </c>
@@ -2612,7 +2886,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>214</v>
+      </c>
       <c r="B94" t="s">
         <v>100</v>
       </c>
@@ -2629,7 +2906,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>214</v>
+      </c>
       <c r="B95" t="s">
         <v>101</v>
       </c>
@@ -2646,7 +2926,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>214</v>
+      </c>
       <c r="B96" t="s">
         <v>102</v>
       </c>
@@ -2663,7 +2946,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>214</v>
+      </c>
       <c r="B97" t="s">
         <v>103</v>
       </c>
@@ -2680,7 +2966,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>214</v>
+      </c>
       <c r="B98" t="s">
         <v>104</v>
       </c>
@@ -2697,7 +2986,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>214</v>
+      </c>
       <c r="B99" t="s">
         <v>105</v>
       </c>
@@ -2714,7 +3006,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>214</v>
+      </c>
       <c r="B100" t="s">
         <v>106</v>
       </c>
@@ -2731,7 +3026,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>214</v>
+      </c>
       <c r="B101" t="s">
         <v>107</v>
       </c>
@@ -2748,7 +3046,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>214</v>
+      </c>
       <c r="B102" t="s">
         <v>108</v>
       </c>
@@ -2765,7 +3066,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>214</v>
+      </c>
       <c r="B103" t="s">
         <v>109</v>
       </c>
@@ -2782,7 +3086,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>214</v>
+      </c>
       <c r="B104" t="s">
         <v>110</v>
       </c>
@@ -2799,7 +3106,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>214</v>
+      </c>
       <c r="B105" t="s">
         <v>111</v>
       </c>
@@ -2816,7 +3126,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>214</v>
+      </c>
       <c r="B106" t="s">
         <v>112</v>
       </c>
@@ -2833,7 +3146,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>214</v>
+      </c>
       <c r="B107" t="s">
         <v>113</v>
       </c>
@@ -2850,7 +3166,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>214</v>
+      </c>
       <c r="B108" t="s">
         <v>114</v>
       </c>
@@ -2867,7 +3186,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>214</v>
+      </c>
       <c r="B109" t="s">
         <v>115</v>
       </c>
@@ -2884,7 +3206,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>214</v>
+      </c>
       <c r="B110" t="s">
         <v>116</v>
       </c>
@@ -2901,7 +3226,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>214</v>
+      </c>
       <c r="B111" t="s">
         <v>117</v>
       </c>
@@ -2918,7 +3246,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>214</v>
+      </c>
       <c r="B112" t="s">
         <v>118</v>
       </c>
@@ -2935,7 +3266,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>214</v>
+      </c>
       <c r="B113" t="s">
         <v>119</v>
       </c>
@@ -2952,7 +3286,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>214</v>
+      </c>
       <c r="B114" t="s">
         <v>120</v>
       </c>
@@ -2969,7 +3306,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>214</v>
+      </c>
       <c r="B115" t="s">
         <v>121</v>
       </c>
@@ -2986,7 +3326,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>214</v>
+      </c>
       <c r="B116" t="s">
         <v>122</v>
       </c>
@@ -3003,7 +3346,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>214</v>
+      </c>
       <c r="B117" t="s">
         <v>123</v>
       </c>
@@ -3020,7 +3366,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>214</v>
+      </c>
       <c r="B118" t="s">
         <v>124</v>
       </c>
@@ -3037,7 +3386,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>214</v>
+      </c>
       <c r="B119" t="s">
         <v>125</v>
       </c>
@@ -3054,7 +3406,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>214</v>
+      </c>
       <c r="B120" t="s">
         <v>126</v>
       </c>
@@ -3071,7 +3426,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>214</v>
+      </c>
       <c r="B121" t="s">
         <v>127</v>
       </c>
@@ -3088,7 +3446,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>214</v>
+      </c>
       <c r="B122" t="s">
         <v>128</v>
       </c>
@@ -3105,7 +3466,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>214</v>
+      </c>
       <c r="B123" t="s">
         <v>129</v>
       </c>
@@ -3122,7 +3486,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>214</v>
+      </c>
       <c r="B124" t="s">
         <v>130</v>
       </c>
@@ -3139,7 +3506,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>214</v>
+      </c>
       <c r="B125" t="s">
         <v>131</v>
       </c>
@@ -3156,7 +3526,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>214</v>
+      </c>
       <c r="B126" t="s">
         <v>132</v>
       </c>
@@ -3173,7 +3546,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>217</v>
+      </c>
       <c r="B127" t="s">
         <v>133</v>
       </c>
@@ -3190,7 +3566,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>217</v>
+      </c>
       <c r="B128" t="s">
         <v>134</v>
       </c>
@@ -3207,7 +3586,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>217</v>
+      </c>
       <c r="B129" t="s">
         <v>135</v>
       </c>
@@ -3224,7 +3606,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>217</v>
+      </c>
       <c r="B130" t="s">
         <v>136</v>
       </c>
@@ -3241,7 +3626,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>217</v>
+      </c>
       <c r="B131" t="s">
         <v>137</v>
       </c>
@@ -3258,7 +3646,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>217</v>
+      </c>
       <c r="B132" t="s">
         <v>138</v>
       </c>
@@ -3275,7 +3666,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>217</v>
+      </c>
       <c r="B133" t="s">
         <v>139</v>
       </c>
@@ -3292,7 +3686,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>217</v>
+      </c>
       <c r="B134" t="s">
         <v>140</v>
       </c>
@@ -3309,7 +3706,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>217</v>
+      </c>
       <c r="B135" t="s">
         <v>141</v>
       </c>
@@ -3326,7 +3726,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>217</v>
+      </c>
       <c r="B136" t="s">
         <v>142</v>
       </c>
@@ -3343,7 +3746,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>217</v>
+      </c>
       <c r="B137" t="s">
         <v>143</v>
       </c>
@@ -3360,7 +3766,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>217</v>
+      </c>
       <c r="B138" t="s">
         <v>55</v>
       </c>
@@ -3377,7 +3786,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>217</v>
+      </c>
       <c r="B139" t="s">
         <v>144</v>
       </c>
@@ -3394,7 +3806,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>217</v>
+      </c>
       <c r="B140" t="s">
         <v>145</v>
       </c>
@@ -3411,7 +3826,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>217</v>
+      </c>
       <c r="B141" t="s">
         <v>146</v>
       </c>
@@ -3428,7 +3846,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>217</v>
+      </c>
       <c r="B142" t="s">
         <v>147</v>
       </c>
@@ -3445,7 +3866,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>217</v>
+      </c>
       <c r="B143" t="s">
         <v>148</v>
       </c>
@@ -3462,7 +3886,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>217</v>
+      </c>
       <c r="B144" t="s">
         <v>149</v>
       </c>
@@ -3479,7 +3906,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>217</v>
+      </c>
       <c r="B145" t="s">
         <v>150</v>
       </c>
@@ -3496,7 +3926,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>217</v>
+      </c>
       <c r="B146" t="s">
         <v>151</v>
       </c>
@@ -3513,7 +3946,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>218</v>
+      </c>
       <c r="B147" t="s">
         <v>152</v>
       </c>
@@ -3530,7 +3966,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>218</v>
+      </c>
       <c r="B148" t="s">
         <v>153</v>
       </c>
@@ -3547,7 +3986,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>218</v>
+      </c>
       <c r="B149" t="s">
         <v>154</v>
       </c>
@@ -3564,7 +4006,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>218</v>
+      </c>
       <c r="B150" t="s">
         <v>155</v>
       </c>
@@ -3581,7 +4026,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>218</v>
+      </c>
       <c r="B151" t="s">
         <v>156</v>
       </c>
@@ -3598,7 +4046,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>218</v>
+      </c>
       <c r="B152" t="s">
         <v>157</v>
       </c>
@@ -3615,7 +4066,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>218</v>
+      </c>
       <c r="B153" t="s">
         <v>158</v>
       </c>
@@ -3632,7 +4086,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>218</v>
+      </c>
       <c r="B154" t="s">
         <v>159</v>
       </c>
@@ -3649,7 +4106,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>218</v>
+      </c>
       <c r="B155" t="s">
         <v>160</v>
       </c>
@@ -3666,7 +4126,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>218</v>
+      </c>
       <c r="B156" t="s">
         <v>161</v>
       </c>
@@ -3683,7 +4146,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>218</v>
+      </c>
       <c r="B157" t="s">
         <v>162</v>
       </c>
@@ -3700,7 +4166,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>218</v>
+      </c>
       <c r="B158" t="s">
         <v>163</v>
       </c>
@@ -3717,7 +4186,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>218</v>
+      </c>
       <c r="B159" t="s">
         <v>164</v>
       </c>
@@ -3734,7 +4206,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>218</v>
+      </c>
       <c r="B160" t="s">
         <v>165</v>
       </c>
@@ -3751,7 +4226,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>218</v>
+      </c>
       <c r="B161" t="s">
         <v>166</v>
       </c>
@@ -3768,7 +4246,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>218</v>
+      </c>
       <c r="B162" t="s">
         <v>167</v>
       </c>
@@ -3785,7 +4266,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>218</v>
+      </c>
       <c r="B163" t="s">
         <v>168</v>
       </c>
@@ -3802,7 +4286,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>218</v>
+      </c>
       <c r="B164" t="s">
         <v>169</v>
       </c>
@@ -3819,7 +4306,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>216</v>
+      </c>
       <c r="B165" t="s">
         <v>170</v>
       </c>
@@ -3836,7 +4326,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>216</v>
+      </c>
       <c r="B166" t="s">
         <v>171</v>
       </c>
@@ -3853,44 +4346,53 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>216</v>
+      </c>
       <c r="B167" t="s">
+        <v>154</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>216</v>
+      </c>
+      <c r="B168" t="s">
         <v>172</v>
       </c>
-      <c r="C167">
-        <v>0</v>
-      </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="E167">
-        <v>0</v>
-      </c>
-      <c r="F167" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B168" t="s">
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="F168" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>216</v>
+      </c>
+      <c r="B169" t="s">
         <v>173</v>
       </c>
-      <c r="C168">
-        <v>0</v>
-      </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
-      <c r="E168">
-        <v>0</v>
-      </c>
-      <c r="F168" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B169" t="s">
-        <v>154</v>
-      </c>
       <c r="C169">
         <v>0</v>
       </c>
@@ -3904,7 +4406,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>216</v>
+      </c>
       <c r="B170" t="s">
         <v>174</v>
       </c>
@@ -3921,7 +4426,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>216</v>
+      </c>
       <c r="B171" t="s">
         <v>175</v>
       </c>
@@ -3938,7 +4446,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>216</v>
+      </c>
       <c r="B172" t="s">
         <v>176</v>
       </c>
@@ -3955,7 +4466,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>216</v>
+      </c>
       <c r="B173" t="s">
         <v>177</v>
       </c>
@@ -3972,7 +4486,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>216</v>
+      </c>
       <c r="B174" t="s">
         <v>178</v>
       </c>
@@ -3989,7 +4506,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>216</v>
+      </c>
       <c r="B175" t="s">
         <v>179</v>
       </c>
@@ -4006,7 +4526,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>216</v>
+      </c>
       <c r="B176" t="s">
         <v>180</v>
       </c>
@@ -4023,7 +4546,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>216</v>
+      </c>
       <c r="B177" t="s">
         <v>181</v>
       </c>
@@ -4040,7 +4566,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>216</v>
+      </c>
       <c r="B178" t="s">
         <v>182</v>
       </c>
@@ -4057,7 +4586,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>216</v>
+      </c>
       <c r="B179" t="s">
         <v>183</v>
       </c>
@@ -4074,7 +4606,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>216</v>
+      </c>
       <c r="B180" t="s">
         <v>184</v>
       </c>
@@ -4091,7 +4626,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>215</v>
+      </c>
       <c r="B181" t="s">
         <v>185</v>
       </c>
@@ -4108,7 +4646,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>215</v>
+      </c>
       <c r="B182" t="s">
         <v>186</v>
       </c>
@@ -4125,7 +4666,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>215</v>
+      </c>
       <c r="B183" t="s">
         <v>187</v>
       </c>
@@ -4142,7 +4686,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>215</v>
+      </c>
       <c r="B184" t="s">
         <v>188</v>
       </c>
@@ -4159,7 +4706,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>215</v>
+      </c>
       <c r="B185" t="s">
         <v>189</v>
       </c>
@@ -4176,7 +4726,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>215</v>
+      </c>
       <c r="B186" t="s">
         <v>190</v>
       </c>
@@ -4193,44 +4746,53 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>215</v>
+      </c>
       <c r="B187" t="s">
+        <v>154</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
+      <c r="F187" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>215</v>
+      </c>
+      <c r="B188" t="s">
         <v>191</v>
       </c>
-      <c r="C187">
-        <v>0</v>
-      </c>
-      <c r="D187">
-        <v>0</v>
-      </c>
-      <c r="E187">
-        <v>0</v>
-      </c>
-      <c r="F187" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B188" t="s">
+      <c r="C188">
+        <v>0</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <v>0</v>
+      </c>
+      <c r="F188" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>215</v>
+      </c>
+      <c r="B189" t="s">
         <v>192</v>
       </c>
-      <c r="C188">
-        <v>0</v>
-      </c>
-      <c r="D188">
-        <v>0</v>
-      </c>
-      <c r="E188">
-        <v>0</v>
-      </c>
-      <c r="F188" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B189" t="s">
-        <v>154</v>
-      </c>
       <c r="C189">
         <v>0</v>
       </c>
@@ -4244,7 +4806,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>215</v>
+      </c>
       <c r="B190" t="s">
         <v>193</v>
       </c>
@@ -4261,7 +4826,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>215</v>
+      </c>
       <c r="B191" t="s">
         <v>194</v>
       </c>
@@ -4278,7 +4846,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>215</v>
+      </c>
       <c r="B192" t="s">
         <v>195</v>
       </c>
@@ -4295,7 +4866,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>215</v>
+      </c>
       <c r="B193" t="s">
         <v>196</v>
       </c>
@@ -4312,7 +4886,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>215</v>
+      </c>
       <c r="B194" t="s">
         <v>197</v>
       </c>
@@ -4329,7 +4906,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>215</v>
+      </c>
       <c r="B195" t="s">
         <v>198</v>
       </c>
@@ -4346,7 +4926,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>215</v>
+      </c>
       <c r="B196" t="s">
         <v>199</v>
       </c>
@@ -4363,7 +4946,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>215</v>
+      </c>
       <c r="B197" t="s">
         <v>200</v>
       </c>
@@ -4380,7 +4966,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>215</v>
+      </c>
       <c r="B198" t="s">
         <v>201</v>
       </c>
@@ -4397,7 +4986,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>215</v>
+      </c>
       <c r="B199" t="s">
         <v>202</v>
       </c>
@@ -4414,7 +5006,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>215</v>
+      </c>
       <c r="B200" t="s">
         <v>203</v>
       </c>
@@ -4431,7 +5026,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>215</v>
+      </c>
       <c r="B201" t="s">
         <v>204</v>
       </c>
@@ -4448,7 +5046,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>215</v>
+      </c>
       <c r="B202" t="s">
         <v>205</v>
       </c>
@@ -4465,7 +5066,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>217</v>
+      </c>
       <c r="B203" t="s">
         <v>206</v>
       </c>
@@ -4482,7 +5086,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>217</v>
+      </c>
       <c r="B204" t="s">
         <v>207</v>
       </c>
@@ -4499,7 +5106,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="205" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>217</v>
+      </c>
       <c r="B205" t="s">
         <v>208</v>
       </c>
@@ -4516,7 +5126,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>217</v>
+      </c>
       <c r="B206" t="s">
         <v>209</v>
       </c>
@@ -4533,7 +5146,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>217</v>
+      </c>
       <c r="B207" t="s">
         <v>210</v>
       </c>
@@ -4550,7 +5166,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>217</v>
+      </c>
       <c r="B208" t="s">
         <v>211</v>
       </c>
@@ -4567,7 +5186,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>217</v>
+      </c>
       <c r="B209" t="s">
         <v>212</v>
       </c>
@@ -4584,7 +5206,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>217</v>
+      </c>
       <c r="B210" t="s">
         <v>213</v>
       </c>
@@ -4598,40 +5223,6 @@
         <v>0</v>
       </c>
       <c r="F210" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B211" t="s">
-        <v>214</v>
-      </c>
-      <c r="C211">
-        <v>0</v>
-      </c>
-      <c r="D211">
-        <v>0</v>
-      </c>
-      <c r="E211">
-        <v>0</v>
-      </c>
-      <c r="F211" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="212" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B212" t="s">
-        <v>215</v>
-      </c>
-      <c r="C212">
-        <v>0</v>
-      </c>
-      <c r="D212">
-        <v>0</v>
-      </c>
-      <c r="E212">
-        <v>0</v>
-      </c>
-      <c r="F212" t="s">
         <v>8</v>
       </c>
     </row>

--- a/dados_projeto.xlsx
+++ b/dados_projeto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9050f00462f35375/Desktop/PYTHON/Projeto_Enxoval/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{61F9F760-CB75-4513-AE38-A32BB50E1E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DAF5E58-8A92-4FAF-AC12-98532E19C70D}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{61F9F760-CB75-4513-AE38-A32BB50E1E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B349ABC2-9574-49A5-86EF-EAC31CE48067}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,6 @@
     <t>Quantidade</t>
   </si>
   <si>
-    <t>Preço Unitário.</t>
-  </si>
-  <si>
     <t>Preço Total</t>
   </si>
   <si>
@@ -677,6 +674,9 @@
   </si>
   <si>
     <t>Banheiro</t>
+  </si>
+  <si>
+    <t>Preço Unitário</t>
   </si>
 </sst>
 </file>
@@ -729,6 +729,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1034,24 +1038,24 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1063,15 +1067,15 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1083,15 +1087,15 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1103,15 +1107,15 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1123,15 +1127,15 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1143,15 +1147,15 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1163,15 +1167,15 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1183,15 +1187,15 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1203,15 +1207,15 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1223,15 +1227,15 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1243,15 +1247,15 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1263,15 +1267,15 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1283,15 +1287,15 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1303,15 +1307,15 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1323,15 +1327,15 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1343,15 +1347,15 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1363,15 +1367,15 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1383,15 +1387,15 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1403,15 +1407,15 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1423,15 +1427,15 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1443,15 +1447,15 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1463,15 +1467,15 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1483,15 +1487,15 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1503,15 +1507,15 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1523,15 +1527,15 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1543,15 +1547,15 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1563,15 +1567,15 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1583,15 +1587,15 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1603,15 +1607,15 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1623,15 +1627,15 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1643,15 +1647,15 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1663,15 +1667,15 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1683,15 +1687,15 @@
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1703,15 +1707,15 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1723,15 +1727,15 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1743,15 +1747,15 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -1763,15 +1767,15 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1783,15 +1787,15 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1803,15 +1807,15 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -1823,15 +1827,15 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1843,15 +1847,15 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1863,15 +1867,15 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1883,15 +1887,15 @@
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1903,15 +1907,15 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1923,15 +1927,15 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1943,15 +1947,15 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1963,15 +1967,15 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1983,15 +1987,15 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2003,15 +2007,15 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -2023,15 +2027,15 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2043,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2063,15 +2067,15 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2083,15 +2087,15 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2103,15 +2107,15 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2123,15 +2127,15 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2143,15 +2147,15 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2163,15 +2167,15 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2183,15 +2187,15 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2203,15 +2207,15 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2223,15 +2227,15 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2243,15 +2247,15 @@
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2263,15 +2267,15 @@
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2283,15 +2287,15 @@
         <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2303,15 +2307,15 @@
         <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2323,15 +2327,15 @@
         <v>0</v>
       </c>
       <c r="F65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2343,15 +2347,15 @@
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -2363,15 +2367,15 @@
         <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2383,15 +2387,15 @@
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2403,15 +2407,15 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2423,15 +2427,15 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2443,15 +2447,15 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2463,15 +2467,15 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2483,15 +2487,15 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2503,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2523,15 +2527,15 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2543,15 +2547,15 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2563,15 +2567,15 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2583,15 +2587,15 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2603,15 +2607,15 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2623,15 +2627,15 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2643,15 +2647,15 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2663,15 +2667,15 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2683,15 +2687,15 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B84" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2703,15 +2707,15 @@
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2723,15 +2727,15 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2743,15 +2747,15 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2763,15 +2767,15 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2783,15 +2787,15 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2803,15 +2807,15 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B90" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2823,15 +2827,15 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2843,15 +2847,15 @@
         <v>0</v>
       </c>
       <c r="F91" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2863,15 +2867,15 @@
         <v>0</v>
       </c>
       <c r="F92" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B93" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2883,15 +2887,15 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2903,15 +2907,15 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2923,15 +2927,15 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B96" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2943,15 +2947,15 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B97" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2963,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2983,15 +2987,15 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -3003,15 +3007,15 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B100" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -3023,15 +3027,15 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -3043,15 +3047,15 @@
         <v>0</v>
       </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -3063,15 +3067,15 @@
         <v>0</v>
       </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B103" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -3083,15 +3087,15 @@
         <v>0</v>
       </c>
       <c r="F103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B104" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -3103,15 +3107,15 @@
         <v>0</v>
       </c>
       <c r="F104" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B105" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -3123,15 +3127,15 @@
         <v>0</v>
       </c>
       <c r="F105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B106" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -3143,15 +3147,15 @@
         <v>0</v>
       </c>
       <c r="F106" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -3163,15 +3167,15 @@
         <v>0</v>
       </c>
       <c r="F107" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B108" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -3183,15 +3187,15 @@
         <v>0</v>
       </c>
       <c r="F108" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B109" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -3203,15 +3207,15 @@
         <v>0</v>
       </c>
       <c r="F109" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B110" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -3223,15 +3227,15 @@
         <v>0</v>
       </c>
       <c r="F110" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B111" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -3243,15 +3247,15 @@
         <v>0</v>
       </c>
       <c r="F111" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B112" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -3263,15 +3267,15 @@
         <v>0</v>
       </c>
       <c r="F112" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B113" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -3283,15 +3287,15 @@
         <v>0</v>
       </c>
       <c r="F113" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B114" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -3303,15 +3307,15 @@
         <v>0</v>
       </c>
       <c r="F114" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B115" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -3323,15 +3327,15 @@
         <v>0</v>
       </c>
       <c r="F115" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B116" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3343,15 +3347,15 @@
         <v>0</v>
       </c>
       <c r="F116" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B117" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -3363,15 +3367,15 @@
         <v>0</v>
       </c>
       <c r="F117" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -3383,15 +3387,15 @@
         <v>0</v>
       </c>
       <c r="F118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B119" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -3403,15 +3407,15 @@
         <v>0</v>
       </c>
       <c r="F119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B120" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3423,15 +3427,15 @@
         <v>0</v>
       </c>
       <c r="F120" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3443,15 +3447,15 @@
         <v>0</v>
       </c>
       <c r="F121" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B122" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3463,15 +3467,15 @@
         <v>0</v>
       </c>
       <c r="F122" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3483,15 +3487,15 @@
         <v>0</v>
       </c>
       <c r="F123" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3503,15 +3507,15 @@
         <v>0</v>
       </c>
       <c r="F124" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -3523,15 +3527,15 @@
         <v>0</v>
       </c>
       <c r="F125" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -3543,15 +3547,15 @@
         <v>0</v>
       </c>
       <c r="F126" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -3563,15 +3567,15 @@
         <v>0</v>
       </c>
       <c r="F127" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B128" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -3583,15 +3587,15 @@
         <v>0</v>
       </c>
       <c r="F128" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B129" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -3603,15 +3607,15 @@
         <v>0</v>
       </c>
       <c r="F129" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3623,15 +3627,15 @@
         <v>0</v>
       </c>
       <c r="F130" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B131" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3643,15 +3647,15 @@
         <v>0</v>
       </c>
       <c r="F131" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B132" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3663,15 +3667,15 @@
         <v>0</v>
       </c>
       <c r="F132" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B133" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3683,15 +3687,15 @@
         <v>0</v>
       </c>
       <c r="F133" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B134" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3703,15 +3707,15 @@
         <v>0</v>
       </c>
       <c r="F134" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B135" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3723,15 +3727,15 @@
         <v>0</v>
       </c>
       <c r="F135" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B136" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3743,15 +3747,15 @@
         <v>0</v>
       </c>
       <c r="F136" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B137" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3763,15 +3767,15 @@
         <v>0</v>
       </c>
       <c r="F137" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B138" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3783,15 +3787,15 @@
         <v>0</v>
       </c>
       <c r="F138" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B139" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3803,15 +3807,15 @@
         <v>0</v>
       </c>
       <c r="F139" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B140" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3823,15 +3827,15 @@
         <v>0</v>
       </c>
       <c r="F140" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B141" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3843,15 +3847,15 @@
         <v>0</v>
       </c>
       <c r="F141" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B142" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3863,15 +3867,15 @@
         <v>0</v>
       </c>
       <c r="F142" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B143" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3883,15 +3887,15 @@
         <v>0</v>
       </c>
       <c r="F143" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B144" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3903,15 +3907,15 @@
         <v>0</v>
       </c>
       <c r="F144" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B145" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3923,15 +3927,15 @@
         <v>0</v>
       </c>
       <c r="F145" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B146" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3943,15 +3947,15 @@
         <v>0</v>
       </c>
       <c r="F146" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B147" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3963,15 +3967,15 @@
         <v>0</v>
       </c>
       <c r="F147" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3983,15 +3987,15 @@
         <v>0</v>
       </c>
       <c r="F148" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B149" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -4003,15 +4007,15 @@
         <v>0</v>
       </c>
       <c r="F149" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B150" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -4023,15 +4027,15 @@
         <v>0</v>
       </c>
       <c r="F150" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B151" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -4043,15 +4047,15 @@
         <v>0</v>
       </c>
       <c r="F151" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B152" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -4063,15 +4067,15 @@
         <v>0</v>
       </c>
       <c r="F152" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B153" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -4083,15 +4087,15 @@
         <v>0</v>
       </c>
       <c r="F153" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B154" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -4103,15 +4107,15 @@
         <v>0</v>
       </c>
       <c r="F154" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B155" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -4123,15 +4127,15 @@
         <v>0</v>
       </c>
       <c r="F155" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B156" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -4143,15 +4147,15 @@
         <v>0</v>
       </c>
       <c r="F156" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B157" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -4163,15 +4167,15 @@
         <v>0</v>
       </c>
       <c r="F157" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B158" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -4183,15 +4187,15 @@
         <v>0</v>
       </c>
       <c r="F158" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B159" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -4203,15 +4207,15 @@
         <v>0</v>
       </c>
       <c r="F159" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B160" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -4223,15 +4227,15 @@
         <v>0</v>
       </c>
       <c r="F160" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B161" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -4243,15 +4247,15 @@
         <v>0</v>
       </c>
       <c r="F161" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B162" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -4263,15 +4267,15 @@
         <v>0</v>
       </c>
       <c r="F162" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B163" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -4283,15 +4287,15 @@
         <v>0</v>
       </c>
       <c r="F163" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B164" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -4303,15 +4307,15 @@
         <v>0</v>
       </c>
       <c r="F164" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B165" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -4323,15 +4327,15 @@
         <v>0</v>
       </c>
       <c r="F165" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B166" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -4343,15 +4347,15 @@
         <v>0</v>
       </c>
       <c r="F166" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B167" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -4363,15 +4367,15 @@
         <v>0</v>
       </c>
       <c r="F167" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B168" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -4383,15 +4387,15 @@
         <v>0</v>
       </c>
       <c r="F168" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B169" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -4403,15 +4407,15 @@
         <v>0</v>
       </c>
       <c r="F169" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B170" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -4423,15 +4427,15 @@
         <v>0</v>
       </c>
       <c r="F170" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B171" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -4443,15 +4447,15 @@
         <v>0</v>
       </c>
       <c r="F171" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B172" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -4463,15 +4467,15 @@
         <v>0</v>
       </c>
       <c r="F172" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B173" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -4483,15 +4487,15 @@
         <v>0</v>
       </c>
       <c r="F173" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B174" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -4503,15 +4507,15 @@
         <v>0</v>
       </c>
       <c r="F174" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B175" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -4523,15 +4527,15 @@
         <v>0</v>
       </c>
       <c r="F175" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B176" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -4543,15 +4547,15 @@
         <v>0</v>
       </c>
       <c r="F176" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B177" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -4563,15 +4567,15 @@
         <v>0</v>
       </c>
       <c r="F177" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B178" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -4583,15 +4587,15 @@
         <v>0</v>
       </c>
       <c r="F178" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B179" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4603,15 +4607,15 @@
         <v>0</v>
       </c>
       <c r="F179" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B180" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4623,15 +4627,15 @@
         <v>0</v>
       </c>
       <c r="F180" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B181" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4643,15 +4647,15 @@
         <v>0</v>
       </c>
       <c r="F181" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B182" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4663,15 +4667,15 @@
         <v>0</v>
       </c>
       <c r="F182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B183" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4683,15 +4687,15 @@
         <v>0</v>
       </c>
       <c r="F183" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B184" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4703,15 +4707,15 @@
         <v>0</v>
       </c>
       <c r="F184" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B185" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4723,15 +4727,15 @@
         <v>0</v>
       </c>
       <c r="F185" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B186" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4743,15 +4747,15 @@
         <v>0</v>
       </c>
       <c r="F186" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B187" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4763,15 +4767,15 @@
         <v>0</v>
       </c>
       <c r="F187" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B188" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4783,15 +4787,15 @@
         <v>0</v>
       </c>
       <c r="F188" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B189" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4803,15 +4807,15 @@
         <v>0</v>
       </c>
       <c r="F189" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B190" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -4823,15 +4827,15 @@
         <v>0</v>
       </c>
       <c r="F190" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B191" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -4843,15 +4847,15 @@
         <v>0</v>
       </c>
       <c r="F191" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -4863,15 +4867,15 @@
         <v>0</v>
       </c>
       <c r="F192" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B193" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -4883,15 +4887,15 @@
         <v>0</v>
       </c>
       <c r="F193" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B194" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -4903,15 +4907,15 @@
         <v>0</v>
       </c>
       <c r="F194" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B195" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -4923,15 +4927,15 @@
         <v>0</v>
       </c>
       <c r="F195" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B196" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -4943,15 +4947,15 @@
         <v>0</v>
       </c>
       <c r="F196" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B197" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -4963,15 +4967,15 @@
         <v>0</v>
       </c>
       <c r="F197" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B198" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -4983,15 +4987,15 @@
         <v>0</v>
       </c>
       <c r="F198" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B199" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -5003,15 +5007,15 @@
         <v>0</v>
       </c>
       <c r="F199" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B200" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -5023,15 +5027,15 @@
         <v>0</v>
       </c>
       <c r="F200" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B201" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -5043,15 +5047,15 @@
         <v>0</v>
       </c>
       <c r="F201" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B202" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -5063,15 +5067,15 @@
         <v>0</v>
       </c>
       <c r="F202" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B203" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -5083,15 +5087,15 @@
         <v>0</v>
       </c>
       <c r="F203" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B204" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -5103,15 +5107,15 @@
         <v>0</v>
       </c>
       <c r="F204" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B205" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -5123,15 +5127,15 @@
         <v>0</v>
       </c>
       <c r="F205" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B206" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -5143,15 +5147,15 @@
         <v>0</v>
       </c>
       <c r="F206" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B207" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -5163,15 +5167,15 @@
         <v>0</v>
       </c>
       <c r="F207" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B208" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -5183,15 +5187,15 @@
         <v>0</v>
       </c>
       <c r="F208" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B209" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -5203,15 +5207,15 @@
         <v>0</v>
       </c>
       <c r="F209" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B210" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -5223,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="F210" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
